--- a/testdata/Login.xlsx
+++ b/testdata/Login.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Sales Force\Automation\stp-automation-test\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A96425A7-7604-4A02-A418-ED12B18A9041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D18D067D-3BD1-4646-A7D3-B0A2778FF8B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Superadmin" sheetId="1" r:id="rId1"/>
     <sheet name="AdminCompany" sheetId="3" r:id="rId2"/>
+    <sheet name="Sales" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="11">
   <si>
     <t>email</t>
   </si>
@@ -62,6 +63,12 @@
   </si>
   <si>
     <t>Welcome back, Fauzan Azimah!</t>
+  </si>
+  <si>
+    <t>santi.nurmala@yopmail.com</t>
+  </si>
+  <si>
+    <t>Welcome back, Santi Nurmala!</t>
   </si>
 </sst>
 </file>
@@ -477,4 +484,46 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AC43FC8-7BCE-4AB4-B6D6-1344B64B41B1}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="29.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{AF4D698B-466E-4FC4-9803-F1817E818F4A}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
+</worksheet>
 </file>
--- a/testdata/Login.xlsx
+++ b/testdata/Login.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Sales Force\Automation\stp-automation-test\testdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Sales Force\Automation\sales-force-automation-test\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D18D067D-3BD1-4646-A7D3-B0A2778FF8B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8A85839-C94D-422A-9DFC-B335D7FC35C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Superadmin" sheetId="1" r:id="rId1"/>
@@ -65,10 +65,10 @@
     <t>Welcome back, Fauzan Azimah!</t>
   </si>
   <si>
-    <t>santi.nurmala@yopmail.com</t>
-  </si>
-  <si>
     <t>Welcome back, Santi Nurmala!</t>
+  </si>
+  <si>
+    <t>fajarsetiawan@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -404,15 +404,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -423,7 +423,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -447,15 +447,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BBAD8D7-5FD9-4749-BFE6-7F3B0A3F590B}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -466,7 +466,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -489,15 +489,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AC43FC8-7BCE-4AB4-B6D6-1344B64B41B1}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -508,15 +508,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
         <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
